--- a/Analysed/GPT/Combined_Analysis_Summary_gpt5.3Instant.xlsx
+++ b/Analysed/GPT/Combined_Analysis_Summary_gpt5.3Instant.xlsx
@@ -1,38 +1,129 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LLM_Gauge\VLM_gauge\Analysed\GPT\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_39735B47C8B6D552A4B88B159EA564A3C4068BD3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="2625" yWindow="2100" windowWidth="20025" windowHeight="10545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overall_Statistics" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed_Metrics" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Overall_Statistics" sheetId="1" r:id="rId1"/>
+    <sheet name="Detailed_Metrics" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Combined Mean ± SD</t>
+  </si>
+  <si>
+    <t>MAE</t>
+  </si>
+  <si>
+    <t>3.8200 ± 3.9124</t>
+  </si>
+  <si>
+    <t>RMSE</t>
+  </si>
+  <si>
+    <t>4.1138 ± 4.0407</t>
+  </si>
+  <si>
+    <t>TMS</t>
+  </si>
+  <si>
+    <t>0.5415 ± 0.2750</t>
+  </si>
+  <si>
+    <t>group_tag</t>
+  </si>
+  <si>
+    <t>sequence_id</t>
+  </si>
+  <si>
+    <t>Valid_Samples</t>
+  </si>
+  <si>
+    <t>dial</t>
+  </si>
+  <si>
+    <t>V1_5 divisions_per_second</t>
+  </si>
+  <si>
+    <t>V4_33 divisions_per_second</t>
+  </si>
+  <si>
+    <t>V5_50 divisions_per_second</t>
+  </si>
+  <si>
+    <t>depth</t>
+  </si>
+  <si>
+    <t>V3_17 divisions_per_second</t>
+  </si>
+  <si>
+    <t>V6_100 divisions_per_second</t>
+  </si>
+  <si>
+    <t>linear</t>
+  </si>
+  <si>
+    <t>V2_0.5 divisions_per_second</t>
+  </si>
+  <si>
+    <t>V3_0.8 divisions_per_second</t>
+  </si>
+  <si>
+    <t>V4_1.7 divisions_per_second</t>
+  </si>
+  <si>
+    <t>V5_2.5 divisions_per_second</t>
+  </si>
+  <si>
+    <t>V7_10 divisions_per_second</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,93 +138,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -421,277 +462,295 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Combined Mean ± SD</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>MAE</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>3.9659 ± 3.9717</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>RMSE</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>4.2024 ± 4.0552</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>TMS</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0.4723 ± 0.2786</t>
-        </is>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>group_tag</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>sequence_id</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Valid_Samples</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>MAE</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>RMSE</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>TMS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>dial</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>V1_5 divisions_per_second</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2">
         <v>82</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.1229707317073171</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.130454012082008</v>
-      </c>
-      <c r="F2" t="n">
+      <c r="D2">
+        <v>0.12297073170731709</v>
+      </c>
+      <c r="E2">
+        <v>0.13045401208200799</v>
+      </c>
+      <c r="F2">
         <v>0.8271604938271605</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>dial</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>V4_33 divisions_per_second</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3">
         <v>59</v>
       </c>
-      <c r="D3" t="n">
-        <v>0.7435677966101695</v>
-      </c>
-      <c r="E3" t="n">
+      <c r="D3">
+        <v>0.74356779661016947</v>
+      </c>
+      <c r="E3">
         <v>1.008630850061069</v>
       </c>
-      <c r="F3" t="n">
-        <v>0.7413793103448276</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>dial</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>V5_50 divisions_per_second</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+      <c r="F3">
+        <v>0.74137931034482762</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4">
         <v>42</v>
       </c>
-      <c r="D4" t="n">
-        <v>8.944797619047618</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="D4">
+        <v>8.9447976190476179</v>
+      </c>
+      <c r="E4">
         <v>8.99446006321722</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>depth</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>V1_5 divisions_per_second</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5">
         <v>82</v>
       </c>
-      <c r="D5" t="n">
-        <v>3.304121951219513</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3.364845199933007</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.4197530864197531</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>depth</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>V3_17 divisions_per_second</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
+      <c r="D5">
+        <v>3.3041219512195128</v>
+      </c>
+      <c r="E5">
+        <v>3.3648451999330069</v>
+      </c>
+      <c r="F5">
+        <v>0.41975308641975312</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6">
         <v>43</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>3.206674418604651</v>
       </c>
-      <c r="E6" t="n">
-        <v>3.47892928262251</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.5952380952380952</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>depth</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>V6_100 divisions_per_second</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
+      <c r="E6">
+        <v>3.4789292826225102</v>
+      </c>
+      <c r="F6">
+        <v>0.59523809523809523</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7">
         <v>19</v>
       </c>
-      <c r="D7" t="n">
-        <v>1.386842105263158</v>
-      </c>
-      <c r="E7" t="n">
+      <c r="D7">
+        <v>1.3868421052631581</v>
+      </c>
+      <c r="E7">
         <v>1.77233862749936</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>0.3888888888888889</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>linear</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>V2_10 divisions_per_second</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8">
+        <v>132</v>
+      </c>
+      <c r="D8">
+        <v>4.3006818181818174</v>
+      </c>
+      <c r="E8">
+        <v>5.4307147668412741</v>
+      </c>
+      <c r="F8">
+        <v>0.29007633587786258</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9">
+        <v>83</v>
+      </c>
+      <c r="D9">
+        <v>9.4996385542168671</v>
+      </c>
+      <c r="E9">
+        <v>9.8746048266210487</v>
+      </c>
+      <c r="F9">
+        <v>0.74390243902439024</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10">
+        <v>58</v>
+      </c>
+      <c r="D10">
+        <v>0.24120689655172409</v>
+      </c>
+      <c r="E10">
+        <v>0.28043992533898932</v>
+      </c>
+      <c r="F10">
+        <v>0.73684210526315785</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11">
+        <v>51</v>
+      </c>
+      <c r="D11">
+        <v>0.21745098039215671</v>
+      </c>
+      <c r="E11">
+        <v>0.24941893256440789</v>
+      </c>
+      <c r="F11">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12">
         <v>49</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D12">
         <v>10.05204081632653</v>
       </c>
-      <c r="E8" t="n">
-        <v>10.66704107548679</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.3333333333333333</v>
+      <c r="E12">
+        <v>10.667041075486789</v>
+      </c>
+      <c r="F12">
+        <v>0.33333333333333331</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>